--- a/TestData/Convert_TestData.xlsx
+++ b/TestData/Convert_TestData.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>123456</t>
+          <t>12345678</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
